--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136042773</v>
       </c>
       <c r="B12" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136042774</v>
       </c>
       <c r="B13" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136042773</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136042774</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136480991</v>
       </c>
       <c r="B19" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>136480977</v>
       </c>
       <c r="B24" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136480991</v>
       </c>
       <c r="B19" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>136480977</v>
       </c>
       <c r="B24" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136480991</v>
       </c>
       <c r="B19" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>136480977</v>
       </c>
       <c r="B24" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136480991</v>
       </c>
       <c r="B19" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>136480977</v>
       </c>
       <c r="B24" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136480991</v>
       </c>
       <c r="B19" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>136480977</v>
       </c>
       <c r="B24" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
